--- a/event/templates/staged_import_cont.xlsx
+++ b/event/templates/staged_import_cont.xlsx
@@ -677,7 +677,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Мусор в поле соцсети будет очищен автоматически</t>
+          <t>Мусор в поле соцсети будет очищен автоматически; групп соцсетей может быть больше 3 — продолжайте нумерацию (Соцсеть 4, Ссылка 4, ...)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
